--- a/data/demo/registry/registry.xlsx
+++ b/data/demo/registry/registry.xlsx
@@ -1915,7 +1915,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
